--- a/Mission_profile.xlsx
+++ b/Mission_profile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickd\Documents\GitHub\LDG_MOTORI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEF729B-5650-4391-AAC9-C299BA3E3779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391ADCA0-A256-4EBB-93C5-98E794DC5599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>Phase</t>
   </si>
@@ -57,9 +57,6 @@
     <t>6-7</t>
   </si>
   <si>
-    <t>Lunghezza Pista</t>
-  </si>
-  <si>
     <t>Gioia del Colle</t>
   </si>
   <si>
@@ -72,27 +69,15 @@
     <t>Istrana</t>
   </si>
   <si>
-    <t>2 992 m</t>
-  </si>
-  <si>
     <t>42 m</t>
   </si>
   <si>
-    <t>2994 m</t>
-  </si>
-  <si>
     <t>5 m</t>
   </si>
   <si>
-    <t>2620 m</t>
-  </si>
-  <si>
     <t>7 m</t>
   </si>
   <si>
-    <t>2349.50 m</t>
-  </si>
-  <si>
     <t>362 m</t>
   </si>
   <si>
@@ -108,24 +93,9 @@
     <t>8-9</t>
   </si>
   <si>
-    <t>Escape dash, at M = 1.5 M and 1000 m for 40 km. Dash should be done as a mil power supercruise if possible</t>
-  </si>
-  <si>
     <t>9-10</t>
   </si>
   <si>
-    <t>Perform a combat air patrol loiter for 5 min at 5000 m and Mach number for best endurance</t>
-  </si>
-  <si>
-    <t>Supersonic penetration at 5000 m and M=1.5 to combat arena. Range = 100 km. Penetration should be done as a military power supercruise if possible</t>
-  </si>
-  <si>
-    <t>Descend to 5000 m. No range/fuel/time credit for descent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combat is modeled by the following:                                                                                          Fire 2 Meteor;                                                                                                          Perform one 360 deg, 5g sustained turn at 5000 m and M = 1.6 m;                                                                                                                     Perform two 360 deg, 5 g sustained turn at 5000 m and M = 0.9;  Accelerate from M = 0.8 to M = 1.60 at 5000 m in maximum power;                                Fire 2 Sidewinder and 1/2 of ammunition.                                                                   No range credit is given for combat maneuvers.                             </t>
-  </si>
-  <si>
     <t>Using mil power, perform a minimum time climb to BCM/BCA. (If the initial energy height exceeds the final, a constant energy height maneuver may be used. No distance credit for the climb.)</t>
   </si>
   <si>
@@ -138,20 +108,32 @@
     <t>11-12</t>
   </si>
   <si>
-    <t>Descend to 1000 m. No range/fuel/time credit for descent.</t>
-  </si>
-  <si>
     <t>12-13</t>
   </si>
   <si>
-    <t>Loiter 20 min at 1000 m and Mach number for best endurance</t>
-  </si>
-  <si>
     <t>13-14</t>
   </si>
   <si>
-    <r>
-      <t>Warm-up and takeoff, field is at 362 m ASL, with air temperature of 29.8 C. Takeoff ground roll plus 3 s rotation distance must be &lt;= 2994 m on wet, hard surface runway (</t>
+    <t>Mission profile by phases</t>
+  </si>
+  <si>
+    <t>Perfomance</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Payload</t>
+  </si>
+  <si>
+    <t>Takeoff distance</t>
+  </si>
+  <si>
+    <r>
+      <t>Warm-up and takeoff, field is at 362 m ASL, with air temperature of 29.8 C. Takeoff ground roll plus 3 s rotation distance must be &lt;= 700 m on wet, hard surface runway (</t>
     </r>
     <r>
       <rPr>
@@ -223,7 +205,7 @@
   </si>
   <si>
     <r>
-      <t>Descend and land, field is at 362 m ASL, air temperature is 29.8 C. A 3 s free roll plus braking distance must be &lt;=2994 m. On wet, hard surface runway (μ</t>
+      <t>Descend and land, field is at 362 m ASL, air temperature is 29.8 C. A 3 s free roll plus braking distance must be &lt;=700 m. On wet, hard surface runway (μ</t>
     </r>
     <r>
       <rPr>
@@ -279,12 +261,138 @@
       <t>STALL</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">Service Ceiling </t>
+  </si>
+  <si>
+    <t>&lt;700 m</t>
+  </si>
+  <si>
+    <t>&lt; 700 m</t>
+  </si>
+  <si>
+    <t>Brakes off to lift off</t>
+  </si>
+  <si>
+    <t>&lt; 8 s</t>
+  </si>
+  <si>
+    <t>Acceleration</t>
+  </si>
+  <si>
+    <t>Max Mach number at altitude</t>
+  </si>
+  <si>
+    <t>Max Mach number at sea level</t>
+  </si>
+  <si>
+    <t>1.25 at 0 m ASL</t>
+  </si>
+  <si>
+    <t>2.0 at 12192 m ASL (40000 ft)</t>
+  </si>
+  <si>
+    <t>&gt; 16764 m ASL (50000 ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range </t>
+  </si>
+  <si>
+    <t>2900 km</t>
+  </si>
+  <si>
+    <t>Seats</t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>Design shall reduce to minimum, practical levels the aircraft's radar, infrared, visual, acoustical, and electromagnetic signatures</t>
+  </si>
+  <si>
+    <t>Landing distance</t>
+  </si>
+  <si>
+    <t>Supercruise requirement</t>
+  </si>
+  <si>
+    <r>
+      <t>Max flight altitude</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Mach 1.1 at 12192 m (40000 ft)
+</t>
+  </si>
+  <si>
+    <t>19812 m (65,000 ft)</t>
+  </si>
+  <si>
+    <t>Initial climb speed</t>
+  </si>
+  <si>
+    <t>255 m/s (Brakes off to 10668 m (35000 ft) / M1.5 &lt;2.5 min (150 s))</t>
+  </si>
+  <si>
+    <t>3 MBDA Meteor (BVRAAM)
+3 AIM-120 AMRAAM (BVRAAM)
+2 IRIS-T (SRAAM)
+2 AIM-9 Sidewinder (SRAAM)
+150 rounds of 27 mm ammunition for Mauser BK-27
+1 x 1000 L fuel drop tank</t>
+  </si>
+  <si>
+    <t>Loiter 20 min at 3000 m and Mach number for best endurance</t>
+  </si>
+  <si>
+    <t>Perform a Defensive Counter-Air Combat Air Patrol loiter for 5 min at 10000 m and Mach number for best endurance</t>
+  </si>
+  <si>
+    <t>Descend to 10000 m. No range/fuel/time credit for descent.</t>
+  </si>
+  <si>
+    <t>Supersonic penetration at 10000 m and M=1.6 to combat arena. Range = 100 km. Penetration should be done as a military power supercruise if possible.</t>
+  </si>
+  <si>
+    <t>Escape dash, at M = 1.4 M and 10000 m for 40 km. Dash should be done as a mil power supercruise if possible</t>
+  </si>
+  <si>
+    <t>Descend to 3000 m. No range/fuel/time credit for descent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mach 0.8 to mach 1.8 at 10000 m
+Mach 0.3 (200 kts or 103 m/s) to Mach 1.0 in 30 s at sea level
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combat is modeled by the following:                                                                                          Fire 3 Meteor;                                                                                                          Perform one 360 deg, 5g sustained turn at 10000 m and M = 1.6 m;                                                                                                                     Perform two 360 deg, 9 g sustained turn at 10000 m and M = 0.8;  Accelerate from M = 0.8 to M = 1.80 at 10000 m in maximum power;                                Fire 2 Sidewinder and 1/2 of ammunition.                                                                   No range credit is given for combat maneuvers. 
+Conditions at the end of the combat are M=1.4 at 10000 m.                            </t>
+  </si>
+  <si>
+    <t>Sustained g level</t>
+  </si>
+  <si>
+    <t>n=5 at Mach 1.6/10000 m
+n=9 at Mach 0.8/10000 m</t>
+  </si>
+  <si>
+    <t>Government-Furnished Equipment</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,8 +427,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,6 +459,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,34 +515,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -419,60 +543,89 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -753,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:K30"/>
+  <dimension ref="B3:T30"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -762,191 +915,313 @@
     <col min="5" max="5" width="38.21875" customWidth="1"/>
     <col min="10" max="10" width="19.88671875" customWidth="1"/>
     <col min="11" max="11" width="59.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" customWidth="1"/>
+    <col min="15" max="15" width="35.33203125" customWidth="1"/>
+    <col min="16" max="16" width="55.109375" customWidth="1"/>
+    <col min="20" max="20" width="46.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" ht="15" thickBot="1"/>
-    <row r="5" spans="2:11" ht="15" thickBot="1">
-      <c r="B5" s="4" t="s">
+    <row r="3" spans="2:20" ht="15" thickBot="1"/>
+    <row r="4" spans="2:20" ht="21.6" thickBot="1">
+      <c r="J4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="O4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="10"/>
+      <c r="T4" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" ht="15" thickBot="1">
+      <c r="J5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="21"/>
+    </row>
+    <row r="6" spans="2:20" ht="87" thickBot="1">
+      <c r="B6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="13"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="J6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="T6" s="21"/>
+    </row>
+    <row r="7" spans="2:20" ht="43.2">
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="J7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T7" s="21"/>
+    </row>
+    <row r="8" spans="2:20" ht="28.8">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="2" t="s">
+      <c r="C8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="J8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T8" s="21"/>
+    </row>
+    <row r="9" spans="2:20">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="J9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S9" s="18"/>
+      <c r="T9" s="21"/>
+    </row>
+    <row r="10" spans="2:20" ht="28.8">
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="J10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="T10" s="21"/>
+    </row>
+    <row r="11" spans="2:20" ht="43.2">
+      <c r="J11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T11" s="21"/>
+    </row>
+    <row r="12" spans="2:20" ht="133.19999999999999" customHeight="1">
+      <c r="J12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="S12" s="19"/>
+    </row>
+    <row r="13" spans="2:20" ht="28.8">
+      <c r="J13" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="K13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="43.2">
+      <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="15" thickBot="1"/>
-    <row r="14" spans="2:11">
-      <c r="J14" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" ht="28.8">
+      <c r="J15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" ht="45.6" customHeight="1">
+      <c r="J16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="10:16" ht="45.6" customHeight="1">
+      <c r="J17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="10:16" ht="52.8" customHeight="1">
+      <c r="J18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="10:16">
+      <c r="O19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P19" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="45.6" customHeight="1">
-      <c r="J15" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" ht="43.8" customHeight="1">
-      <c r="J16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="10:11" ht="27.6" customHeight="1">
-      <c r="J17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="10:11">
-      <c r="J18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="10:11" ht="37.200000000000003" customHeight="1">
-      <c r="J19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="10:11" ht="44.4" customHeight="1">
-      <c r="J20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="10:11" ht="104.4" customHeight="1">
-      <c r="J21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="10:11" ht="41.4" customHeight="1">
-      <c r="J22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="10:11" ht="53.4" customHeight="1">
-      <c r="J23" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="10:11" ht="28.8">
-      <c r="J24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="10:11">
-      <c r="J25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="10:11">
-      <c r="J26" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="10:11" ht="44.4">
-      <c r="J27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="10:11">
-      <c r="J28" s="11"/>
-      <c r="K28" s="12"/>
-    </row>
-    <row r="29" spans="10:11">
-      <c r="J29" s="11"/>
-      <c r="K29" s="12"/>
-    </row>
-    <row r="30" spans="10:11">
-      <c r="J30" s="11"/>
-      <c r="K30" s="12"/>
+    <row r="20" spans="10:16" ht="37.200000000000003" customHeight="1">
+      <c r="O20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="10:16" ht="44.4" customHeight="1"/>
+    <row r="22" spans="10:16" ht="104.4" customHeight="1"/>
+    <row r="23" spans="10:16" ht="41.4" customHeight="1"/>
+    <row r="24" spans="10:16" ht="53.4" customHeight="1"/>
+    <row r="28" spans="10:16">
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="10:16">
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" spans="10:16">
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="O4:P4"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="J17" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Mission_profile.xlsx
+++ b/Mission_profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickd\Documents\GitHub\LDG_MOTORI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Francesco Daniele/Documents/GitHub/LDG_MOTORI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391ADCA0-A256-4EBB-93C5-98E794DC5599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A9DA52-BCD0-864F-9E1E-79877F78DC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>Phase</t>
   </si>
@@ -387,12 +387,52 @@
   <si>
     <t>Government-Furnished Equipment</t>
   </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>Armament/stores</t>
+  </si>
+  <si>
+    <t>D.1.1</t>
+  </si>
+  <si>
+    <t>D.1.2</t>
+  </si>
+  <si>
+    <t>D.1.3</t>
+  </si>
+  <si>
+    <t>AMRAAM:
+Launch weight: 326 lbf</t>
+  </si>
+  <si>
+    <t>25 mm cannon:
+Cannon weight: 270 lbf
+Ammunition feed system weight (500 rounds): 405 lbf
+Ammunition (25 mm) weight (fired rounds): 550 lbf
+Casings weight (returned): 198 lbf</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>AIM-9L Sidewinder Missile:
+Launch weight: 191 lbf (</t>
+  </si>
+  <si>
+    <t>Diameter, deployed: 15.6 ft
+Time from initiation to full deployment (during free roll): 2.5s</t>
+  </si>
+  <si>
+    <t>Drag chute:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,14 +475,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
@@ -475,7 +507,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -521,19 +553,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -554,6 +573,51 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -569,7 +633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -589,43 +653,56 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -906,37 +983,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:T30"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B3:U30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" customWidth="1"/>
-    <col min="5" max="5" width="38.21875" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="38.1640625" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
     <col min="11" max="11" width="59.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="12.5546875" customWidth="1"/>
+    <col min="13" max="13" width="10.5" customWidth="1"/>
+    <col min="14" max="14" width="12.5" customWidth="1"/>
     <col min="15" max="15" width="35.33203125" customWidth="1"/>
-    <col min="16" max="16" width="55.109375" customWidth="1"/>
-    <col min="20" max="20" width="46.88671875" customWidth="1"/>
+    <col min="16" max="16" width="55.1640625" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" customWidth="1"/>
+    <col min="21" max="21" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:20" ht="15" thickBot="1"/>
-    <row r="4" spans="2:20" ht="21.6" thickBot="1">
-      <c r="J4" s="9" t="s">
+    <row r="3" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:21" ht="22" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="O4" s="9" t="s">
+      <c r="K4" s="17"/>
+      <c r="O4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="10"/>
-      <c r="T4" s="20" t="s">
+      <c r="P4" s="17"/>
+      <c r="S4" s="21" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="5" spans="2:20" ht="15" thickBot="1">
+      <c r="T4" s="22"/>
+      <c r="U4" s="23"/>
+    </row>
+    <row r="5" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J5" s="7" t="s">
         <v>0</v>
       </c>
@@ -949,16 +1029,21 @@
       <c r="P5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="T5" s="21"/>
-    </row>
-    <row r="6" spans="2:20" ht="87" thickBot="1">
-      <c r="B6" s="14" t="s">
+      <c r="S5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="U5" s="20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="97" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="10"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="J6" s="6" t="s">
@@ -973,16 +1058,22 @@
       <c r="P6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="T6" s="21"/>
-    </row>
-    <row r="7" spans="2:20" ht="43.2">
-      <c r="B7" s="16" t="s">
+      <c r="S6" s="15"/>
+      <c r="T6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" ht="32" x14ac:dyDescent="0.2">
+      <c r="B7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="9"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="J7" s="1" t="s">
@@ -997,16 +1088,22 @@
       <c r="P7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T7" s="21"/>
-    </row>
-    <row r="8" spans="2:20" ht="28.8">
+      <c r="S7" s="15"/>
+      <c r="T7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="80" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="9"/>
       <c r="J8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1019,16 +1116,22 @@
       <c r="P8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="T8" s="21"/>
-    </row>
-    <row r="9" spans="2:20">
+      <c r="S8" s="15"/>
+      <c r="T8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12"/>
+      <c r="D9" s="8"/>
       <c r="J9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,17 +1144,22 @@
       <c r="P9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S9" s="18"/>
-      <c r="T9" s="21"/>
-    </row>
-    <row r="10" spans="2:20" ht="28.8">
+      <c r="S9" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="T9" s="14"/>
+      <c r="U9" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="48" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="9"/>
       <c r="J10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1064,9 +1172,13 @@
       <c r="P10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="T10" s="21"/>
-    </row>
-    <row r="11" spans="2:20" ht="43.2">
+      <c r="S10" s="15"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="48" x14ac:dyDescent="0.2">
       <c r="J11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1079,9 +1191,11 @@
       <c r="P11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T11" s="21"/>
-    </row>
-    <row r="12" spans="2:20" ht="133.19999999999999" customHeight="1">
+      <c r="S11" s="18"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+    </row>
+    <row r="12" spans="2:21" ht="133.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1094,9 +1208,8 @@
       <c r="P12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S12" s="19"/>
-    </row>
-    <row r="13" spans="2:20" ht="28.8">
+    </row>
+    <row r="13" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="J13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1110,7 +1223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:20" ht="43.2">
+    <row r="14" spans="2:21" ht="48" x14ac:dyDescent="0.2">
       <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1124,7 +1237,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:20" ht="28.8">
+    <row r="15" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="J15" s="1" t="s">
         <v>24</v>
       </c>
@@ -1138,7 +1251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:20" ht="45.6" customHeight="1">
+    <row r="16" spans="2:21" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1152,7 +1265,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="10:16" ht="45.6" customHeight="1">
+    <row r="17" spans="10:16" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1166,7 +1279,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="10:16" ht="52.8" customHeight="1">
+    <row r="18" spans="10:16" ht="52.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J18" s="1" t="s">
         <v>28</v>
       </c>
@@ -1180,7 +1293,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="10:16">
+    <row r="19" spans="10:16" x14ac:dyDescent="0.2">
       <c r="O19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1188,7 +1301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="10:16" ht="37.200000000000003" customHeight="1">
+    <row r="20" spans="10:16" ht="37.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1196,24 +1309,25 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="10:16" ht="44.4" customHeight="1"/>
-    <row r="22" spans="10:16" ht="104.4" customHeight="1"/>
-    <row r="23" spans="10:16" ht="41.4" customHeight="1"/>
-    <row r="24" spans="10:16" ht="53.4" customHeight="1"/>
-    <row r="28" spans="10:16">
+    <row r="21" spans="10:16" ht="44.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="10:16" ht="104.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="10:16" ht="41.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="10:16" ht="53.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="10:16" x14ac:dyDescent="0.2">
       <c r="J28" s="4"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="10:16">
+    <row r="29" spans="10:16" x14ac:dyDescent="0.2">
       <c r="J29" s="4"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="10:16">
+    <row r="30" spans="10:16" x14ac:dyDescent="0.2">
       <c r="J30" s="4"/>
       <c r="K30" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="S4:U4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="O4:P4"/>
   </mergeCells>

--- a/Mission_profile.xlsx
+++ b/Mission_profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Francesco Daniele/Documents/GitHub/LDG_MOTORI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elisa\OneDrive\Documenti\GitHub\LDG_MOTORI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A9DA52-BCD0-864F-9E1E-79877F78DC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB093F5-3D94-4FFF-AB6A-4E7256266858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -633,7 +633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -678,30 +678,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -984,39 +980,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:U30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="38.1640625" customWidth="1"/>
-    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.77734375" customWidth="1"/>
     <col min="11" max="11" width="59.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="12.5" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" customWidth="1"/>
     <col min="15" max="15" width="35.33203125" customWidth="1"/>
-    <col min="16" max="16" width="55.1640625" customWidth="1"/>
+    <col min="16" max="16" width="55.109375" customWidth="1"/>
     <col min="20" max="20" width="10.33203125" customWidth="1"/>
-    <col min="21" max="21" width="47.6640625" customWidth="1"/>
+    <col min="21" max="21" width="56.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:21" ht="22" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J4" s="16" t="s">
+    <row r="3" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J4" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="O4" s="16" t="s">
+      <c r="K4" s="22"/>
+      <c r="O4" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="17"/>
-      <c r="S4" s="21" t="s">
+      <c r="P4" s="22"/>
+      <c r="S4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="T4" s="22"/>
-      <c r="U4" s="23"/>
-    </row>
-    <row r="5" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="T4" s="19"/>
+      <c r="U4" s="20"/>
+    </row>
+    <row r="5" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J5" s="7" t="s">
         <v>0</v>
       </c>
@@ -1029,14 +1025,14 @@
       <c r="P5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="20" t="s">
+      <c r="S5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="20" t="s">
+      <c r="U5" s="17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="97" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
@@ -1066,7 +1062,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1096,7 +1092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="80" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" ht="72" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1124,7 +1120,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1144,7 +1140,7 @@
       <c r="P9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S9" s="24" t="s">
+      <c r="S9" s="14" t="s">
         <v>79</v>
       </c>
       <c r="T9" s="14"/>
@@ -1152,7 +1148,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="48" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1178,7 +1174,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="48" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1191,11 +1187,10 @@
       <c r="P11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S11" s="18"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-    </row>
-    <row r="12" spans="2:21" ht="133.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+    </row>
+    <row r="12" spans="2:21" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1209,7 +1204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1223,7 +1218,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:21" ht="48" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1237,7 +1232,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:21" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J15" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,7 +1246,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:21" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" ht="45.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1265,7 +1260,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="10:16" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="10:16" ht="45.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1279,7 +1274,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="10:16" ht="52.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="10:16" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J18" s="1" t="s">
         <v>28</v>
       </c>
@@ -1293,7 +1288,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="10:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:16" x14ac:dyDescent="0.3">
       <c r="O19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1301,7 +1296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="10:16" ht="37.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="10:16" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1309,19 +1304,19 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="10:16" ht="44.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="10:16" ht="104.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="10:16" ht="41.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="10:16" ht="53.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="10:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="10:16" ht="44.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="10:16" ht="104.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="10:16" ht="41.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="10:16" ht="53.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="10:16" x14ac:dyDescent="0.3">
       <c r="J28" s="4"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="10:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="10:16" x14ac:dyDescent="0.3">
       <c r="J29" s="4"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="10:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="10:16" x14ac:dyDescent="0.3">
       <c r="J30" s="4"/>
       <c r="K30" s="5"/>
     </row>

--- a/Mission_profile.xlsx
+++ b/Mission_profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elisa\OneDrive\Documenti\GitHub\LDG_MOTORI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Francesco Daniele/Documents/GitHub/LDG_MOTORI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB093F5-3D94-4FFF-AB6A-4E7256266858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B39F9EB-8E2B-E746-A9CC-631D5624CD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22320" yWindow="0" windowWidth="22320" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -403,22 +403,7 @@
     <t>D.1.3</t>
   </si>
   <si>
-    <t>AMRAAM:
-Launch weight: 326 lbf</t>
-  </si>
-  <si>
-    <t>25 mm cannon:
-Cannon weight: 270 lbf
-Ammunition feed system weight (500 rounds): 405 lbf
-Ammunition (25 mm) weight (fired rounds): 550 lbf
-Casings weight (returned): 198 lbf</t>
-  </si>
-  <si>
     <t>D.2</t>
-  </si>
-  <si>
-    <t>AIM-9L Sidewinder Missile:
-Launch weight: 191 lbf (</t>
   </si>
   <si>
     <t>Diameter, deployed: 15.6 ft
@@ -426,6 +411,21 @@
   </si>
   <si>
     <t>Drag chute:</t>
+  </si>
+  <si>
+    <t>AIM-9L Sidewinder Missile:
+Launch weight: 191 lbf (86,6361 kg)</t>
+  </si>
+  <si>
+    <t>AMRAAM:
+Launch weight: 326 lbf (147,8711 kg)</t>
+  </si>
+  <si>
+    <t>25 mm cannon:
+Cannon weight: 270 lbf (122,4699 kg)
+Ammunition feed system weight (500 rounds): 405 lbf (183,7049 kg)
+Ammunition (25 mm) weight (fired rounds): 550 lbf (249,4758 kg)
+Casings weight (returned): 198 lbf (89,8113 kg)</t>
   </si>
 </sst>
 </file>
@@ -980,24 +980,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:U30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" customWidth="1"/>
-    <col min="5" max="5" width="38.109375" customWidth="1"/>
-    <col min="10" max="10" width="19.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="38.1640625" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
     <col min="11" max="11" width="59.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.5" customWidth="1"/>
+    <col min="14" max="14" width="12.5" customWidth="1"/>
     <col min="15" max="15" width="35.33203125" customWidth="1"/>
-    <col min="16" max="16" width="55.109375" customWidth="1"/>
+    <col min="16" max="16" width="55.1640625" customWidth="1"/>
     <col min="20" max="20" width="10.33203125" customWidth="1"/>
-    <col min="21" max="21" width="56.21875" customWidth="1"/>
+    <col min="21" max="21" width="56.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:21" ht="22" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J4" s="21" t="s">
         <v>29</v>
       </c>
@@ -1012,7 +1012,7 @@
       <c r="T4" s="19"/>
       <c r="U4" s="20"/>
     </row>
-    <row r="5" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J5" s="7" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" ht="97" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="B7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1089,10 +1089,10 @@
         <v>75</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21" ht="72" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="80" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1117,10 +1117,10 @@
         <v>76</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1141,14 +1141,14 @@
         <v>47</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="T9" s="14"/>
       <c r="U9" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1171,10 +1171,10 @@
       <c r="S10" s="15"/>
       <c r="T10" s="14"/>
       <c r="U10" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="48" x14ac:dyDescent="0.2">
       <c r="J11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
     </row>
-    <row r="12" spans="2:21" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="133.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="J13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" ht="48" x14ac:dyDescent="0.2">
       <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="J15" s="1" t="s">
         <v>24</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:21" ht="45.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="10:16" ht="45.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="10:16" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="10:16" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:16" ht="52.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J18" s="1" t="s">
         <v>28</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="10:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="10:16" x14ac:dyDescent="0.2">
       <c r="O19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="10:16" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="10:16" ht="37.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1304,19 +1304,19 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="10:16" ht="44.55" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="10:16" ht="104.55" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="10:16" ht="41.55" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="10:16" ht="53.55" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="10:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:16" ht="44.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="10:16" ht="104.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="10:16" ht="41.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="10:16" ht="53.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="10:16" x14ac:dyDescent="0.2">
       <c r="J28" s="4"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="10:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="10:16" x14ac:dyDescent="0.2">
       <c r="J29" s="4"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="10:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="10:16" x14ac:dyDescent="0.2">
       <c r="J30" s="4"/>
       <c r="K30" s="5"/>
     </row>

--- a/Mission_profile.xlsx
+++ b/Mission_profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Francesco Daniele/Documents/GitHub/LDG_MOTORI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B39F9EB-8E2B-E746-A9CC-631D5624CD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2B5E64-483D-5342-A9A3-9A0E6D5B7385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22320" yWindow="0" windowWidth="22320" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="82">
   <si>
     <t>Phase</t>
   </si>
@@ -388,44 +388,36 @@
     <t>Government-Furnished Equipment</t>
   </si>
   <si>
-    <t>D.1</t>
-  </si>
-  <si>
-    <t>Armament/stores</t>
-  </si>
-  <si>
-    <t>D.1.1</t>
-  </si>
-  <si>
-    <t>D.1.2</t>
-  </si>
-  <si>
-    <t>D.1.3</t>
-  </si>
-  <si>
-    <t>D.2</t>
-  </si>
-  <si>
-    <t>Diameter, deployed: 15.6 ft
-Time from initiation to full deployment (during free roll): 2.5s</t>
-  </si>
-  <si>
-    <t>Drag chute:</t>
-  </si>
-  <si>
-    <t>AIM-9L Sidewinder Missile:
-Launch weight: 191 lbf (86,6361 kg)</t>
-  </si>
-  <si>
-    <t>AMRAAM:
-Launch weight: 326 lbf (147,8711 kg)</t>
-  </si>
-  <si>
-    <t>25 mm cannon:
-Cannon weight: 270 lbf (122,4699 kg)
-Ammunition feed system weight (500 rounds): 405 lbf (183,7049 kg)
-Ammunition (25 mm) weight (fired rounds): 550 lbf (249,4758 kg)
-Casings weight (returned): 198 lbf (89,8113 kg)</t>
+    <t>MBDA Meteor: 419 lb (190 kg)</t>
+  </si>
+  <si>
+    <t>AIM-120 AMRAAM: 356 lb (161.5 kg)</t>
+  </si>
+  <si>
+    <t>IRIS-T: 193 lb (87.4 kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIM-9 Sidewinder: 189,6 lb (86 kg) </t>
+  </si>
+  <si>
+    <t>3x</t>
+  </si>
+  <si>
+    <t>2x</t>
+  </si>
+  <si>
+    <t>27 mm ammunition for Mauser BK-27:  1.14 lb (516 g):
+Proiettile: 0.5732 lb (260 g)
+Bossolo: 516 - 260 = 0.5644 lb (256 g)</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Weight per Unit</t>
+  </si>
+  <si>
+    <t>150x</t>
   </si>
 </sst>
 </file>
@@ -481,7 +473,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,8 +498,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -585,10 +583,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -600,7 +598,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -609,31 +607,14 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -677,27 +658,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -705,6 +692,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC6E0B4"/>
+      <color rgb="FF92D051"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -998,19 +991,19 @@
   <sheetData>
     <row r="3" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:21" ht="22" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="22"/>
-      <c r="O4" s="21" t="s">
+      <c r="K4" s="18"/>
+      <c r="O4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="22"/>
-      <c r="S4" s="18" t="s">
+      <c r="P4" s="18"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="T4" s="19"/>
-      <c r="U4" s="20"/>
+      <c r="U4" s="16"/>
     </row>
     <row r="5" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J5" s="7" t="s">
@@ -1025,11 +1018,12 @@
       <c r="P5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="U5" s="17" t="s">
-        <v>73</v>
+      <c r="S5" s="20"/>
+      <c r="T5" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="U5" s="24" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="97" thickBot="1" x14ac:dyDescent="0.25">
@@ -1054,12 +1048,12 @@
       <c r="P6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="S6" s="15"/>
-      <c r="T6" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>80</v>
+      <c r="S6" s="20"/>
+      <c r="T6" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="U6" s="15" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:21" ht="32" x14ac:dyDescent="0.2">
@@ -1084,15 +1078,15 @@
       <c r="P7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="15"/>
+      <c r="S7" s="20"/>
       <c r="T7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21" ht="80" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1112,12 +1106,12 @@
       <c r="P8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="15"/>
+      <c r="S8" s="20"/>
       <c r="T8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="2:21" ht="16" x14ac:dyDescent="0.2">
@@ -1140,15 +1134,14 @@
       <c r="P9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="T9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="T9" s="14"/>
-      <c r="U9" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" ht="32" x14ac:dyDescent="0.2">
+      <c r="U9" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="48" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1168,8 +1161,10 @@
       <c r="P10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="S10" s="15"/>
-      <c r="T10" s="14"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="U10" s="3" t="s">
         <v>78</v>
       </c>
@@ -1187,8 +1182,9 @@
       <c r="P11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="20"/>
     </row>
     <row r="12" spans="2:21" ht="133.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J12" s="1" t="s">
@@ -1203,6 +1199,9 @@
       <c r="P12" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="S12" s="20"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="20"/>
     </row>
     <row r="13" spans="2:21" ht="32" x14ac:dyDescent="0.2">
       <c r="J13" s="1" t="s">
@@ -1322,9 +1321,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="S4:U4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="O4:P4"/>
+    <mergeCell ref="T4:U4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
